--- a/data/trans_orig/IP07A10-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07A10-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido disfrutar de su tiempo libre en 2007 (tasa de respuesta: 99,4%)</t>
+          <t>Menores según la frecuencia de haber podido disfrutar de su tiempo libre, percibida por el adulto en 2007 (tasa de respuesta: 99,4%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8395</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18702</t>
+          <t>19214</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16853</t>
+          <t>17110</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30060</t>
+          <t>30642</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29082</t>
+          <t>29070</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45237</t>
+          <t>46029</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,78%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28704</t>
+          <t>28094</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41241</t>
+          <t>41053</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37005</t>
+          <t>36390</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51175</t>
+          <t>51023</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>70183</t>
+          <t>68737</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>89381</t>
+          <t>88375</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>61,02%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10970</t>
+          <t>10708</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23026</t>
+          <t>21984</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8483</t>
+          <t>8819</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19072</t>
+          <t>19584</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>22093</t>
+          <t>21921</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38031</t>
+          <t>37073</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,6%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22871</t>
+          <t>23395</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37647</t>
+          <t>37678</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22051</t>
+          <t>21973</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35705</t>
+          <t>36303</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47852</t>
+          <t>49341</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68842</t>
+          <t>70196</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>34,54%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44730</t>
+          <t>44926</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60437</t>
+          <t>60473</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40268</t>
+          <t>40588</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55584</t>
+          <t>55766</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>89258</t>
+          <t>87911</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>111253</t>
+          <t>111025</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>54,63%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13823</t>
+          <t>14291</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26879</t>
+          <t>26735</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14355</t>
+          <t>14603</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27056</t>
+          <t>27170</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>32015</t>
+          <t>31910</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>50563</t>
+          <t>49753</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,48%</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5186</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>668</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6473</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3322</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>3951</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5372</t>
+          <t>4675</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15903</t>
+          <t>15925</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27629</t>
+          <t>27576</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17256</t>
+          <t>18064</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30043</t>
+          <t>30415</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36888</t>
+          <t>36699</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54074</t>
+          <t>53764</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,45%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21699</t>
+          <t>21280</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33332</t>
+          <t>33230</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21979</t>
+          <t>21844</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34565</t>
+          <t>35136</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>46026</t>
+          <t>47213</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>63839</t>
+          <t>63984</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,51%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5854</t>
+          <t>5740</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14439</t>
+          <t>14689</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9276</t>
+          <t>9192</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19621</t>
+          <t>19903</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17519</t>
+          <t>16837</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>30551</t>
+          <t>30272</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>23,9%</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4187</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2487</t>
+          <t>2471</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3788</t>
+          <t>3767</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4147</t>
+          <t>3138</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20886</t>
+          <t>20827</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35889</t>
+          <t>36022</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25230</t>
+          <t>24908</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40775</t>
+          <t>40385</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>50250</t>
+          <t>49986</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>71880</t>
+          <t>70558</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,07%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>31008</t>
+          <t>31234</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>47889</t>
+          <t>48158</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>39490</t>
+          <t>39150</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>55249</t>
+          <t>55833</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>75071</t>
+          <t>74071</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>97587</t>
+          <t>95839</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>50,35%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15305</t>
+          <t>15430</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29052</t>
+          <t>29345</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12691</t>
+          <t>12434</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>24860</t>
+          <t>25515</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>31553</t>
+          <t>31659</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>50754</t>
+          <t>50444</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,5%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>690</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>5982</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6387</t>
+          <t>5841</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>4749</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4619</t>
+          <t>5097</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>79527</t>
+          <t>79149</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>105804</t>
+          <t>106554</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>94390</t>
+          <t>95263</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>121528</t>
+          <t>121789</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>181738</t>
+          <t>182594</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>219024</t>
+          <t>218298</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,82%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>139684</t>
+          <t>139917</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>167770</t>
+          <t>168441</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>152043</t>
+          <t>154098</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>182171</t>
+          <t>182596</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>300277</t>
+          <t>301328</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>342436</t>
+          <t>341890</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,41%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>56023</t>
+          <t>55413</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>81082</t>
+          <t>80147</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>54556</t>
+          <t>55339</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>76465</t>
+          <t>78063</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>117058</t>
+          <t>115978</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>149372</t>
+          <t>149016</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1581</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8486</t>
+          <t>8824</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>594</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5857</t>
+          <t>5636</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3855,42 +3855,42 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>6431</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>3371</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>11317</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
           <t>1,7%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>6431</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>3338</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>11462</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="W31" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>629</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>5592</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4691</t>
+          <t>4590</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7959</t>
+          <t>7552</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido disfrutar de su tiempo libre en 2012 (tasa de respuesta: 98,02%)</t>
+          <t>Menores según la frecuencia de haber podido disfrutar de su tiempo libre, percibida por el adulto en 2012 (tasa de respuesta: 98,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22990</t>
+          <t>22927</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36362</t>
+          <t>36272</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25796</t>
+          <t>25820</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40520</t>
+          <t>40309</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52115</t>
+          <t>51282</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>71471</t>
+          <t>71891</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,99%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21241</t>
+          <t>22425</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35535</t>
+          <t>35850</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23127</t>
+          <t>23353</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37492</t>
+          <t>37505</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50199</t>
+          <t>50058</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69510</t>
+          <t>69598</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,33%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12101</t>
+          <t>12657</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>4391</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12689</t>
+          <t>12434</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9781</t>
+          <t>9730</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21707</t>
+          <t>21309</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,41%</t>
         </is>
       </c>
     </row>
@@ -4754,7 +4754,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4543</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3462</t>
+          <t>3486</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36938</t>
+          <t>36901</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51760</t>
+          <t>52688</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27117</t>
+          <t>26269</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42549</t>
+          <t>41148</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68215</t>
+          <t>68233</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89659</t>
+          <t>89422</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>45,84%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32843</t>
+          <t>32123</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47276</t>
+          <t>47827</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41651</t>
+          <t>41674</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57403</t>
+          <t>57541</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>77889</t>
+          <t>78630</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>100402</t>
+          <t>100896</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,72%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8375</t>
+          <t>8318</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18527</t>
+          <t>20023</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>7403</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18619</t>
+          <t>18563</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18758</t>
+          <t>18435</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>33344</t>
+          <t>33192</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,01%</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3140</t>
+          <t>3143</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2341</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2869</t>
+          <t>3224</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16982</t>
+          <t>17020</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28665</t>
+          <t>30096</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26381</t>
+          <t>26788</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39875</t>
+          <t>40115</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47741</t>
+          <t>47371</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>65688</t>
+          <t>65275</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>47,98%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24920</t>
+          <t>24401</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37389</t>
+          <t>37892</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16162</t>
+          <t>16257</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28646</t>
+          <t>28109</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43922</t>
+          <t>44174</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61281</t>
+          <t>62191</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>45,71%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>7810</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17587</t>
+          <t>17505</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>8131</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17960</t>
+          <t>17952</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17873</t>
+          <t>17751</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>32353</t>
+          <t>32952</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>24,22%</t>
         </is>
       </c>
     </row>
@@ -6083,7 +6083,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>2683</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2522</t>
+          <t>3261</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>581</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>4819</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>581</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4732</t>
+          <t>4891</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24879</t>
+          <t>25031</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40230</t>
+          <t>40354</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26585</t>
+          <t>25866</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41516</t>
+          <t>41617</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>54900</t>
+          <t>55090</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>78353</t>
+          <t>77471</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,0%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>37256</t>
+          <t>37666</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>54064</t>
+          <t>54107</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>32706</t>
+          <t>31948</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47701</t>
+          <t>48539</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>74533</t>
+          <t>74551</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>97152</t>
+          <t>97081</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,63%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6131</t>
+          <t>6249</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16941</t>
+          <t>17470</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9862</t>
+          <t>9287</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>21654</t>
+          <t>21063</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>18492</t>
+          <t>17933</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>33986</t>
+          <t>33465</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,14%</t>
         </is>
       </c>
     </row>
@@ -6765,7 +6765,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5166</t>
+          <t>4631</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10889</t>
+          <t>9585</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2904</t>
+          <t>2671</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12017</t>
+          <t>11645</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -6878,7 +6878,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3785</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4096</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>114333</t>
+          <t>115550</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>144334</t>
+          <t>144345</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>120177</t>
+          <t>120449</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>150044</t>
+          <t>149008</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>241801</t>
+          <t>244473</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>282877</t>
+          <t>284061</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,44%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>132069</t>
+          <t>131654</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>159882</t>
+          <t>161210</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>124739</t>
+          <t>126948</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>155970</t>
+          <t>157559</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>267474</t>
+          <t>265998</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>309716</t>
+          <t>307420</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,02%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>33249</t>
+          <t>33629</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>53846</t>
+          <t>52840</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>37007</t>
+          <t>37855</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>58264</t>
+          <t>57737</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>76371</t>
+          <t>74989</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>105646</t>
+          <t>103894</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>724</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7176</t>
+          <t>6297</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2723</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12116</t>
+          <t>11899</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>4836</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>14768</t>
+          <t>14651</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -7560,7 +7560,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3734</t>
+          <t>3754</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7263</t>
+          <t>7033</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7540</t>
+          <t>7640</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido disfrutar de su tiempo libre en 2016 (tasa de respuesta: 98,92%)</t>
+          <t>Menores según la frecuencia de haber podido disfrutar de su tiempo libre, percibida por el adulto en 2016 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25830</t>
+          <t>26282</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40510</t>
+          <t>40187</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,82 +8032,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>37,1%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>56,73%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>29961</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>22466</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>37190</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>40,69%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>30,51%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>50,51%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>63000</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>52679</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>72972</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>43,61%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>36,46%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>57,18%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>29961</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>23081</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>37553</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>40,69%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>31,35%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>51,0%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>63000</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>52882</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>73140</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>43,61%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>36,61%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,51%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19191</t>
+          <t>20454</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33508</t>
+          <t>33763</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23462</t>
+          <t>24011</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38634</t>
+          <t>38580</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46893</t>
+          <t>47079</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68190</t>
+          <t>67209</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>46,52%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5086</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15415</t>
+          <t>14963</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6711</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18105</t>
+          <t>18153</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14552</t>
+          <t>14172</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29253</t>
+          <t>28139</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>19,48%</t>
         </is>
       </c>
     </row>
@@ -8361,7 +8361,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3241</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5155</t>
+          <t>5544</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5933</t>
+          <t>6056</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -8474,92 +8474,92 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>4620</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>6,52%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1408</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
           <t>4963</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,01%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1408</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4858</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31877</t>
+          <t>32694</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48470</t>
+          <t>47979</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33949</t>
+          <t>32904</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51824</t>
+          <t>49615</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69763</t>
+          <t>70373</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>92527</t>
+          <t>93659</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,71%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42720</t>
+          <t>42959</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59670</t>
+          <t>59786</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40543</t>
+          <t>41359</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57813</t>
+          <t>58430</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>89201</t>
+          <t>89072</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>112177</t>
+          <t>112286</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,4%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7583</t>
+          <t>7835</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18083</t>
+          <t>18222</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7989</t>
+          <t>8065</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19149</t>
+          <t>19491</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>17876</t>
+          <t>18930</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>33083</t>
+          <t>33670</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>574</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6094</t>
+          <t>6791</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>725</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7518</t>
+          <t>7034</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2348</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10854</t>
+          <t>9660</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -9156,7 +9156,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3712</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3444</t>
+          <t>3466</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4477</t>
+          <t>4844</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27955</t>
+          <t>27586</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41235</t>
+          <t>41685</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30300</t>
+          <t>29739</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44546</t>
+          <t>44631</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62137</t>
+          <t>62510</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>82160</t>
+          <t>82322</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,25%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21434</t>
+          <t>21521</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35047</t>
+          <t>34606</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26104</t>
+          <t>26144</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40325</t>
+          <t>39895</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>51495</t>
+          <t>50658</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>71366</t>
+          <t>70279</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>47,17%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4625</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13398</t>
+          <t>13714</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9062</t>
+          <t>9247</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7793</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>19002</t>
+          <t>19736</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>754</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6397</t>
+          <t>6977</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>759</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6460</t>
+          <t>7328</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2910</t>
+          <t>2996</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>2941</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27814</t>
+          <t>27360</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45339</t>
+          <t>44542</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28393</t>
+          <t>28608</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45014</t>
+          <t>45312</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>60466</t>
+          <t>61870</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>83879</t>
+          <t>84211</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>40,15%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>40057</t>
+          <t>40539</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>57956</t>
+          <t>58744</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>40706</t>
+          <t>39277</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>57384</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>85461</t>
+          <t>85498</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>110900</t>
+          <t>109447</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>52,18%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11263</t>
+          <t>10954</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24578</t>
+          <t>24774</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10611</t>
+          <t>10455</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23610</t>
+          <t>22768</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>24615</t>
+          <t>24932</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>42883</t>
+          <t>42163</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>1554</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7909</t>
+          <t>8630</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10442,7 +10442,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4341</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10457,7 +10457,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10685</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -10520,7 +10520,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5291</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>5268</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>129212</t>
+          <t>128777</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>159040</t>
+          <t>160442</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>130224</t>
+          <t>131036</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>160981</t>
+          <t>160760</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>268850</t>
+          <t>268613</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>310988</t>
+          <t>311359</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,4%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>140063</t>
+          <t>139372</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>169803</t>
+          <t>169610</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>146957</t>
+          <t>146408</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>178309</t>
+          <t>178404</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>294019</t>
+          <t>295945</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>336572</t>
+          <t>341703</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>47,63%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>36892</t>
+          <t>36615</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>58222</t>
+          <t>57644</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>35259</t>
+          <t>34142</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>55314</t>
+          <t>54938</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>76458</t>
+          <t>77435</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>105744</t>
+          <t>109312</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3148</t>
+          <t>3471</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>11887</t>
+          <t>12574</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>3791</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>13813</t>
+          <t>13941</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>8722</t>
+          <t>9026</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>23052</t>
+          <t>22346</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8739</t>
+          <t>8349</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11237,7 +11237,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11252,7 +11252,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>9221</t>
+          <t>9163</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido disfrutar de su tiempo libre en 2023 (tasa de respuesta: 99,79%)</t>
+          <t>Menores según la frecuencia de haber podido disfrutar de su tiempo libre, percibida por el adulto en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39561</t>
+          <t>38789</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49447</t>
+          <t>49491</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44036</t>
+          <t>45399</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>68384</t>
+          <t>69901</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11709,12 +11709,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>88581</t>
+          <t>88792</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>115678</t>
+          <t>115701</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,16%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6734</t>
+          <t>6475</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16705</t>
+          <t>17299</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9966</t>
+          <t>9646</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26709</t>
+          <t>24827</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19335</t>
+          <t>18897</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38321</t>
+          <t>38949</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,32%</t>
         </is>
       </c>
     </row>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3283</t>
+          <t>3360</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27333</t>
+          <t>26714</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2560</t>
+          <t>2569</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27697</t>
+          <t>32794</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11975,7 +11975,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>23,0%</t>
         </is>
       </c>
     </row>
@@ -12116,7 +12116,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2574</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>456</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>4349</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12201,7 +12201,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51778</t>
+          <t>51983</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68320</t>
+          <t>68944</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>83071</t>
+          <t>82651</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>108186</t>
+          <t>106752</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>140155</t>
+          <t>139815</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>170781</t>
+          <t>170126</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,02%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22101</t>
+          <t>21378</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37133</t>
+          <t>36892</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31519</t>
+          <t>32197</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56892</t>
+          <t>56076</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59146</t>
+          <t>58909</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>87724</t>
+          <t>89061</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>36,13%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3309</t>
+          <t>3277</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11491</t>
+          <t>11566</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10148</t>
+          <t>10695</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6813</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18682</t>
+          <t>18971</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -12685,7 +12685,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3749</t>
+          <t>3862</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>756</t>
+          <t>789</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9437</t>
+          <t>8836</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1459</t>
+          <t>782</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9443</t>
+          <t>10255</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2782</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12813,7 +12813,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>858</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7468</t>
+          <t>7949</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12848,7 +12848,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>885</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7941</t>
+          <t>7868</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26052</t>
+          <t>25097</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>72042</t>
+          <t>71748</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55499</t>
+          <t>54562</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>78296</t>
+          <t>79057</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>80243</t>
+          <t>79517</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>143152</t>
+          <t>143526</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>63,01%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39985</t>
+          <t>39862</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>89644</t>
+          <t>91228</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27659</t>
+          <t>27639</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>50746</t>
+          <t>52155</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>75816</t>
+          <t>75081</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>144098</t>
+          <t>140305</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>61,59%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1619</t>
+          <t>1614</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9413</t>
+          <t>9954</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13269,7 +13269,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>896</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8528</t>
+          <t>8640</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3850</t>
+          <t>3663</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14395</t>
+          <t>14657</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3712</t>
+          <t>3297</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13382,7 +13382,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13437,7 +13437,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3003</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13452,7 +13452,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49350</t>
+          <t>49439</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>65604</t>
+          <t>65307</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46094</t>
+          <t>44593</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>63730</t>
+          <t>63054</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>99356</t>
+          <t>100607</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>124546</t>
+          <t>124995</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>65,02%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21327</t>
+          <t>20832</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>35875</t>
+          <t>36010</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>28160</t>
+          <t>28495</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>45473</t>
+          <t>46084</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>51779</t>
+          <t>52807</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>76868</t>
+          <t>76699</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,9%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3327</t>
+          <t>4056</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13316</t>
+          <t>13676</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1456</t>
+          <t>1431</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10435</t>
+          <t>9621</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6872</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>19637</t>
+          <t>18909</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>5175</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14064,7 +14064,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14119,7 +14119,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>5083</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14134,7 +14134,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -14162,7 +14162,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4311</t>
+          <t>4103</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14197,7 +14197,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3663</t>
+          <t>3722</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14212,7 +14212,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>527</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>5532</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14247,7 +14247,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>167819</t>
+          <t>163831</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>238200</t>
+          <t>239073</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>253476</t>
+          <t>252924</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>298778</t>
+          <t>300237</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>438980</t>
+          <t>436115</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>527234</t>
+          <t>526584</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>65,09%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>105311</t>
+          <t>105616</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>183020</t>
+          <t>186935</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,82 +14515,82 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>28,6%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>50,61%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>134263</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>114526</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>157803</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>30,53%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>26,05%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>35,89%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>263567</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>230694</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>325796</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>32,58%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>28,51%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>49,55%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>134263</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>114487</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>158597</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>30,53%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>26,04%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>36,07%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>263567</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>230908</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>328086</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>32,58%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>28,54%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,27%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12260</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>27876</t>
+          <t>28279</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>12078</t>
+          <t>12807</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>41742</t>
+          <t>42646</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>28768</t>
+          <t>28253</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>60262</t>
+          <t>58807</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>850</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>7247</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>764</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9256</t>
+          <t>10563</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14781,7 +14781,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2512</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>13191</t>
+          <t>12367</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>527</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6061</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1714</t>
+          <t>1601</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10247</t>
+          <t>9094</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3242</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>12212</t>
+          <t>12809</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
